--- a/consent_forms/041_swimming_lesson_consent_form--consent_forms.xlsx
+++ b/consent_forms/041_swimming_lesson_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>swimmer_id</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Swimmer's Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter swimmer's name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>parent_id</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Parent's or Guardian's Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter parent/guardian's name</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>swimmer_dob</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Date of Birth</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -594,12 +606,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>emergency_contact_name</t>
+          <t>Emergency Contact's Name</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Name of emergency contact person</t>
+          <t>Enter emergency contact's name</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -611,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
+          <t>emergency_contact_relationship</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Relationship to Swimmer</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mother, Father, Guardian</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -634,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>relationship</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Medical Conditions</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>List of medical conditions</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -662,17 +682,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>emergency_contact_address</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>Emergency Contact's Address</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>List of medical conditions</t>
+          <t>Enter address</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -684,23 +704,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medical_notes</t>
+          <t>emergency_contact_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>medical_notes</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Emergency Contact's Phone Number</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter phone number</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -712,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>swimmer_allergies</t>
+          <t>emergency_contact_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>swimmer_allergies</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Emergency Contact's Email</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter email</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -730,22 +758,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>emergency_contact_address</t>
+          <t>emergency_clearance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>emergency_contact_address</t>
+          <t>Medical Clearance</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Emergency contact address</t>
+          <t>None, True, False</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -762,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
+          <t>emergency_contact_notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Emergency Contact's Notes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter notes</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -785,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>emergency_contact_email</t>
+          <t>swimmer_notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>emergency_contact_email</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Swimmer's Notes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter notes</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -803,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medical_clearance</t>
+          <t>swimmer_signature</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>medical_clearance</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Swimmer's Signature</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Enter signature</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>yes</t>
@@ -826,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>emergency_contact_phone_number</t>
+          <t>emergency_contact_signature</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>emergency_contact_phone_number</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Emergency Contact's Signature</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enter signature</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>yes</t>
@@ -849,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>emergency_contact_phone_extension</t>
+          <t>swimmer_dob_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>emergency_contact_phone_extension</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Swimmer Dob 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>yes</t>
@@ -872,20 +920,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>emergency_contact_email</t>
+          <t>swimmer_dob_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>emergency_contact_email</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Swimmer Dob 3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>yes</t>
@@ -895,205 +947,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>emergency_contact_notes</t>
+          <t>swimmer_dob_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>emergency_contact_notes</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Swimmer Dob 4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>swimmer_notes</t>
+          <t>swimmer_dob_5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>swimmer_notes</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Swimmer Dob 5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>swimmer_signature</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>swimmer_signature</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>emergency_contact_signature</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>emergency_contact_signature</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>swimmer_dob</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>swimmer_dob</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>swimmer_dob</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>swimmer_dob</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>swimmer_dob</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>swimmer_dob</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>swimmer_dob</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>swimmer_dob</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>swimmer_dob</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>swimmer_dob</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1189,7 +1088,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>medical_clearance_choices</t>
+          <t>emergency_clearance_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1206,7 +1105,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>medical_clearance_choices</t>
+          <t>emergency_clearance_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1223,7 +1122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>medical_clearance_choices</t>
+          <t>emergency_clearance_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
